--- a/hourly datasets/cap_gen_year9final.xlsx
+++ b/hourly datasets/cap_gen_year9final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1069567095850491</v>
+        <v>0.1022743441442176</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09043386850983193</v>
+        <v>0.08922528217993425</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1973905780948811</v>
+        <v>0.1914996263241518</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08657203724954163</v>
+        <v>0.08449485533917972</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1935287468345908</v>
+        <v>0.1867691994833973</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07076940770021801</v>
+        <v>0.06674334646533926</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1777261172852672</v>
+        <v>0.1690176906095568</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08794861539697796</v>
+        <v>0.08542301444680317</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +557,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1949053249820271</v>
+        <v>0.1876973585910207</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +567,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01160641164542359</v>
+        <v>0.004873002166792543</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002110497307708295</v>
+        <v>0.0008874123295125567</v>
       </c>
       <c r="D7" t="n">
-        <v>1.469620788740304</v>
+        <v>1.256665973799769</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02056724542427917</v>
+        <v>0.01128168080748437</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007438496073986227</v>
+        <v>0.003132353088457887</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0157743272168608</v>
+        <v>0.00661365124512726</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1185631212304727</v>
+        <v>0.1071473463110101</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +595,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009536076865655638</v>
+        <v>0.001952495908815522</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001926331599393779</v>
+        <v>0.0008039158325896252</v>
       </c>
       <c r="D8" t="n">
-        <v>1.085580795335966</v>
+        <v>0.7646198382847578</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03023052421355057</v>
+        <v>0.02013637314586916</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005754940319859566</v>
+        <v>0.0003756983632874164</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01331721341145166</v>
+        <v>0.003529293454343693</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1164927864507048</v>
+        <v>0.1042268400530331</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +623,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00727739748016039</v>
+        <v>0.0006825203764719581</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001764429781329991</v>
+        <v>0.0007703991115516598</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7613382333757169</v>
+        <v>0.4965022996659167</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01433506537452428</v>
+        <v>0.00978597994435384</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003815499890623111</v>
+        <v>-0.0008286940234306188</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01073929506969786</v>
+        <v>0.002193734776374534</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1142341070652095</v>
+        <v>0.1029568645206895</v>
       </c>
     </row>
     <row r="10">
@@ -651,15 +651,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008847981047940032</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+        <v>0.000954845967853236</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0009709261940528455</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5807312449054687</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.007281026036105187</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.0009499507187873612</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.002859642654493766</v>
+      </c>
       <c r="H10" t="n">
-        <v>0.1158046906329892</v>
+        <v>0.1032291901120708</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +679,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0270930316302893</v>
+        <v>0.02655110147010492</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -677,7 +687,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1340497412153384</v>
+        <v>0.1288254456143225</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +697,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04845712219404096</v>
+        <v>0.04690602322734268</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -695,7 +705,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1554138317790901</v>
+        <v>0.1491803673715603</v>
       </c>
     </row>
     <row r="13">
@@ -705,7 +715,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05989195624476158</v>
+        <v>0.05894301102833688</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -713,7 +723,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1668486658298107</v>
+        <v>0.1612173551725544</v>
       </c>
     </row>
     <row r="14">
@@ -723,7 +733,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06825378053622953</v>
+        <v>0.06761252144258938</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -731,7 +741,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1752104901212787</v>
+        <v>0.1698868655868069</v>
       </c>
     </row>
     <row r="15">
@@ -741,7 +751,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0740785428087717</v>
+        <v>0.07163029936297079</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -749,7 +759,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1810352523938208</v>
+        <v>0.1739046435071884</v>
       </c>
     </row>
     <row r="16">
@@ -759,7 +769,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07898793123304286</v>
+        <v>0.07596353346717592</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -767,7 +777,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.185944640818092</v>
+        <v>0.1782378776113935</v>
       </c>
     </row>
     <row r="17">
@@ -777,7 +787,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07957936531373674</v>
+        <v>0.07711694782985475</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -785,7 +795,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1865360748987859</v>
+        <v>0.1793912919740723</v>
       </c>
     </row>
     <row r="18">
@@ -795,22 +805,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1069567095850491</v>
+        <v>-0.1022743441442176</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01087930151352742</v>
+        <v>0.009927036023224547</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.6302705007023</v>
+        <v>-18.00859047322026</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03755329832689248</v>
+        <v>0.03828806651514288</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1283871727892488</v>
+        <v>-0.1217909630336668</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08552624638084962</v>
+        <v>-0.08275772525476867</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -823,7 +833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08246171007332959</v>
+        <v>0.07964493845441359</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -831,7 +841,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1894184196583787</v>
+        <v>0.1819192825986312</v>
       </c>
     </row>
     <row r="20">
@@ -841,7 +851,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08443691597725367</v>
+        <v>0.08288153968969428</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -849,7 +859,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1913936255623028</v>
+        <v>0.1851558838339118</v>
       </c>
     </row>
     <row r="21">
@@ -859,25 +869,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08744852886512905</v>
+        <v>0.08683264665098818</v>
       </c>
       <c r="C21" t="n">
-        <v>0.008276865909264689</v>
+        <v>0.007758375877687512</v>
       </c>
       <c r="D21" t="n">
-        <v>20.10065263639976</v>
+        <v>20.06773750523188</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05494994659393142</v>
+        <v>0.05332479622178313</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07117535664272361</v>
+        <v>0.07157994042008103</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1037217010875345</v>
+        <v>0.1020853528818952</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1944052384501782</v>
+        <v>0.1891069907952058</v>
       </c>
     </row>
     <row r="22">
@@ -887,7 +897,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09399495848337078</v>
+        <v>0.09180332397715214</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -895,7 +905,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2009516680684199</v>
+        <v>0.1940776681213697</v>
       </c>
     </row>
     <row r="23">
@@ -905,7 +915,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0956437197288324</v>
+        <v>0.09370845682178539</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -913,7 +923,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2026004293138816</v>
+        <v>0.195982800966003</v>
       </c>
     </row>
     <row r="24">
@@ -923,25 +933,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09933894505425432</v>
+        <v>0.09702055340104944</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008991469368418069</v>
+        <v>0.008120647814804581</v>
       </c>
       <c r="D24" t="n">
-        <v>21.88141561751501</v>
+        <v>21.83992653083353</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05500252448082291</v>
+        <v>0.05274039942574813</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08163086045605795</v>
+        <v>0.08105766162749681</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1170470296524511</v>
+        <v>0.112983445174602</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2062956546393035</v>
+        <v>0.199294897545267</v>
       </c>
     </row>
     <row r="25">
@@ -951,25 +961,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1002298850499006</v>
+        <v>0.09782784724552077</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008735023889623637</v>
+        <v>0.008004088309507782</v>
       </c>
       <c r="D25" t="n">
-        <v>22.06344703063166</v>
+        <v>22.17733830298355</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05725570524262481</v>
+        <v>0.05529878252264482</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08304093042708108</v>
+        <v>0.08209553646201058</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1174188396727207</v>
+        <v>0.1135601580290305</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2071865946349497</v>
+        <v>0.2001021913897383</v>
       </c>
     </row>
     <row r="26">
@@ -979,25 +989,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.09919511808624296</v>
+        <v>0.0973441848932047</v>
       </c>
       <c r="C26" t="n">
-        <v>0.009216307508984183</v>
+        <v>0.008541648948075336</v>
       </c>
       <c r="D26" t="n">
-        <v>21.33043148661273</v>
+        <v>21.65364047736667</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06636201394291159</v>
+        <v>0.06246431329151857</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08104689763435589</v>
+        <v>0.08054026266281485</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1173433385381295</v>
+        <v>0.1141481071235947</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2061518276712921</v>
+        <v>0.1996185290374223</v>
       </c>
     </row>
     <row r="27">
@@ -1007,25 +1017,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1022434263271316</v>
+        <v>0.1005550695263345</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009302710074219846</v>
+        <v>0.008429866510306984</v>
       </c>
       <c r="D27" t="n">
-        <v>20.04756509900071</v>
+        <v>20.49443041126871</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07615426964768562</v>
+        <v>0.07696115815278917</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0839287846934087</v>
+        <v>0.08397083945516878</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1205580679608547</v>
+        <v>0.1171392995974997</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2092001359121807</v>
+        <v>0.2028294136705521</v>
       </c>
     </row>
     <row r="28">
@@ -1035,25 +1045,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.09944184158901578</v>
+        <v>0.09754313392680154</v>
       </c>
       <c r="C28" t="n">
-        <v>0.009319826563435848</v>
+        <v>0.007798843217232105</v>
       </c>
       <c r="D28" t="n">
-        <v>18.55880300867425</v>
+        <v>18.99535308392685</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09409764082176228</v>
+        <v>0.09068681842222258</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08106222313164926</v>
+        <v>0.08221377103869845</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1178214600463839</v>
+        <v>0.1128724968149048</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2063985511740649</v>
+        <v>0.1998174780710191</v>
       </c>
     </row>
     <row r="29">
@@ -1063,25 +1073,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01755680487140073</v>
+        <v>0.003361458973601489</v>
       </c>
       <c r="C29" t="n">
-        <v>0.005029041937002473</v>
+        <v>0.0008543567163046094</v>
       </c>
       <c r="D29" t="n">
-        <v>1.490034156925886</v>
+        <v>0.9018896066939093</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01626332096562937</v>
+        <v>0.004967432371742611</v>
       </c>
       <c r="F29" t="n">
-        <v>0.007356858771473115</v>
+        <v>0.001682766925059087</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02775675097132797</v>
+        <v>0.005040151022143734</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1245135144564499</v>
+        <v>0.1056358031178191</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year9final.xlsx
+++ b/hourly datasets/cap_gen_year9final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2326316532862757</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1022743441442176</v>
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09879379741345343</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08922528217993425</v>
+        <v>0.3826689040532499</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1914996263241518</v>
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2488310481804277</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08449485533917972</v>
+        <v>0.3839476876325742</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1867691994833973</v>
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.250109831759752</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06674334646533926</v>
+        <v>0.3624941153769656</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1690176906095568</v>
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2286562595041434</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +566,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08542301444680317</v>
+        <v>0.3704548501251257</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +574,10 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1876973585910207</v>
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2366169942523035</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +587,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004873002166792543</v>
+        <v>0.3689400069917285</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008874123295125567</v>
+        <v>0.003351024962753155</v>
       </c>
       <c r="D7" t="n">
-        <v>1.256665973799769</v>
+        <v>7.675263225990556</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01128168080748437</v>
+        <v>0.02241995981843753</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003132353088457887</v>
+        <v>0.01444248541735852</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00661365124512726</v>
+        <v>0.02759941672537952</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1071473463110101</v>
+        <v>94</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2351021511189062</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +618,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001952495908815522</v>
+        <v>0.4839867787474581</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0008039158325896252</v>
+        <v>0.00971479740990998</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7646198382847578</v>
+        <v>1.474852489137382</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02013637314586916</v>
+        <v>0.7700146095517171</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0003756983632874164</v>
+        <v>-0.01430423150817089</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003529293454343693</v>
+        <v>0.02383842549147683</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1042268400530331</v>
+        <v>122</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3501489228746358</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +649,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0006825203764719581</v>
+        <v>0.4627334225637149</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0007703991115516598</v>
+        <v>0.01257328221863563</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4965022996659167</v>
+        <v>-0.7588774250584791</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00978597994435384</v>
+        <v>0.06105569729175526</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0008286940234306188</v>
+        <v>-0.04562703970894681</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002193734776374534</v>
+        <v>0.003741065229783552</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1029568645206895</v>
+        <v>122</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3288955666908926</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +680,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000954845967853236</v>
+        <v>0.4569738198538734</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009709261940528455</v>
+        <v>0.01865835277700376</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5807312449054687</v>
+        <v>-0.3814578090106402</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007281026036105187</v>
+        <v>0.1132877938185689</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0009499507187873612</v>
+        <v>-0.06204576475253214</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002859642654493766</v>
+        <v>0.01121614879331247</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1032291901120708</v>
+        <v>122</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3231359639810512</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +711,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02655110147010492</v>
+        <v>0.2694907897734683</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +719,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1288254456143225</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1356529339006461</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04690602322734268</v>
+        <v>0.2970430823793107</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +740,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1491803673715603</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1632052265064885</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +753,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05894301102833688</v>
+        <v>0.3109566976452292</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +761,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1612173551725544</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1771188417724069</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +774,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06761252144258938</v>
+        <v>0.3223215366151506</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +782,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1698868655868069</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1884836807423284</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07163029936297079</v>
+        <v>0.3265997443234025</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +803,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1739046435071884</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1927618884505803</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +816,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07596353346717592</v>
+        <v>0.3333159240695941</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +824,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1782378776113935</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1994780681967719</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +837,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07711694782985475</v>
+        <v>0.3383778033024522</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +845,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1793912919740723</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.20453994742963</v>
       </c>
     </row>
     <row r="18">
@@ -805,24 +858,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1022743441442176</v>
+        <v>0.1338378558728222</v>
       </c>
       <c r="C18" t="n">
-        <v>0.009927036023224547</v>
+        <v>0.01029698192566065</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.00859047322026</v>
+        <v>-18.1509373226842</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03828806651514288</v>
+        <v>0.03879373260068358</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1217909630336668</v>
+        <v>-0.1243400386245325</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08275772525476867</v>
+        <v>-0.08385369248608678</v>
       </c>
       <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,7 +889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07964493845441359</v>
+        <v>0.3401207519469476</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +897,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1819192825986312</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2062828960741253</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08288153968969428</v>
+        <v>0.3442205222917926</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +918,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1851558838339118</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2103826664189704</v>
       </c>
     </row>
     <row r="21">
@@ -869,25 +931,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08683264665098818</v>
+        <v>0.3477377378454311</v>
       </c>
       <c r="C21" t="n">
-        <v>0.007758375877687512</v>
+        <v>0.007741435609389409</v>
       </c>
       <c r="D21" t="n">
-        <v>20.06773750523188</v>
+        <v>20.04164090290157</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05332479622178313</v>
+        <v>0.05325453920743359</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07157994042008103</v>
+        <v>0.07146418168769403</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1020853528818952</v>
+        <v>0.1019029970846229</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1891069907952058</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2138998819726089</v>
       </c>
     </row>
     <row r="22">
@@ -897,7 +962,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09180332397715214</v>
+        <v>0.3532362929267626</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -905,7 +970,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1940776681213697</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2193984370539404</v>
       </c>
     </row>
     <row r="23">
@@ -915,7 +983,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.09370845682178539</v>
+        <v>0.3585947512115247</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -923,7 +991,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.195982800966003</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2247568953387025</v>
       </c>
     </row>
     <row r="24">
@@ -933,25 +1004,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09702055340104944</v>
+        <v>0.3643681429447899</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008120647814804581</v>
+        <v>0.008101803429909833</v>
       </c>
       <c r="D24" t="n">
-        <v>21.83992653083353</v>
+        <v>21.80243802895837</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05274039942574813</v>
+        <v>0.05266820930901349</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08105766162749681</v>
+        <v>0.08089453243315982</v>
       </c>
       <c r="G24" t="n">
-        <v>0.112983445174602</v>
+        <v>0.1127462126885783</v>
       </c>
       <c r="H24" t="n">
-        <v>0.199294897545267</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2305302870719676</v>
       </c>
     </row>
     <row r="25">
@@ -961,25 +1035,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.09782784724552077</v>
+        <v>0.3687413264928349</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008004088309507782</v>
+        <v>0.007974322581100469</v>
       </c>
       <c r="D25" t="n">
-        <v>22.17733830298355</v>
+        <v>22.13046462366341</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05529878252264482</v>
+        <v>0.05520648621406829</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08209553646201058</v>
+        <v>0.08187758237330232</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1135601580290305</v>
+        <v>0.1132250110023294</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2001021913897383</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2349034706200127</v>
       </c>
     </row>
     <row r="26">
@@ -989,25 +1066,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0973441848932047</v>
+        <v>0.3706742104966601</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008541648948075336</v>
+        <v>0.008469478380812969</v>
       </c>
       <c r="D26" t="n">
-        <v>21.65364047736667</v>
+        <v>21.58084732609442</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06246431329151857</v>
+        <v>0.06231950455475186</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08054026266281485</v>
+        <v>0.08010459601808739</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1141481071235947</v>
+        <v>0.1134285360916971</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1996185290374223</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2368363546238378</v>
       </c>
     </row>
     <row r="27">
@@ -1017,25 +1097,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1005550695263345</v>
+        <v>0.3752951123687747</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008429866510306984</v>
+        <v>0.008325511825151235</v>
       </c>
       <c r="D27" t="n">
-        <v>20.49443041126871</v>
+        <v>20.41190626191857</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07696115815278917</v>
+        <v>0.07632988719394297</v>
       </c>
       <c r="F27" t="n">
-        <v>0.08397083945516878</v>
+        <v>0.0834550684317102</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1171392995974997</v>
+        <v>0.1162122793028036</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2028294136705521</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2414572564959524</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1128,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.09754313392680154</v>
+        <v>0.3833812016909581</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007798843217232105</v>
+        <v>0.007977071867709426</v>
       </c>
       <c r="D28" t="n">
-        <v>18.99535308392685</v>
+        <v>19.19142313872864</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09068681842222258</v>
+        <v>0.0919101277743247</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08221377103869845</v>
+        <v>0.08345621905122973</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1128724968149048</v>
+        <v>0.1148154704748613</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1998174780710191</v>
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2495433458181359</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1159,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.003361458973601489</v>
+        <v>0.3383263017838057</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0008543567163046094</v>
+        <v>0.01011969748729616</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9018896066939093</v>
+        <v>5.161574875909022</v>
       </c>
       <c r="E29" t="n">
-        <v>0.004967432371742611</v>
+        <v>0.0069114184766263</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001682766925059087</v>
+        <v>0.02348856345550635</v>
       </c>
       <c r="G29" t="n">
-        <v>0.005040151022143734</v>
+        <v>0.06324802913486569</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1056358031178191</v>
+        <v>100</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2044884459109834</v>
       </c>
     </row>
   </sheetData>
